--- a/app/development/catalogo/data/catalogo_nao_mostrar_indice.xlsx
+++ b/app/development/catalogo/data/catalogo_nao_mostrar_indice.xlsx
@@ -20,54 +20,84 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t xml:space="preserve">CÓDIGO</t>
   </si>
   <si>
+    <t xml:space="preserve">DESCRIÇÃO</t>
+  </si>
+  <si>
     <t xml:space="preserve">DESCRIÇÃO DO MATERIAL</t>
   </si>
   <si>
     <t xml:space="preserve">AC</t>
   </si>
   <si>
+    <t xml:space="preserve">Acúmulo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Não Mostrar no índice</t>
   </si>
   <si>
     <t xml:space="preserve">AN</t>
   </si>
   <si>
+    <t xml:space="preserve">Em Análise</t>
+  </si>
+  <si>
     <t xml:space="preserve">OC</t>
   </si>
   <si>
+    <t xml:space="preserve">Ocorrência</t>
+  </si>
+  <si>
     <t xml:space="preserve">RT</t>
   </si>
   <si>
+    <t xml:space="preserve">Retrabalho</t>
+  </si>
+  <si>
     <t xml:space="preserve">INT MOD</t>
   </si>
   <si>
+    <t xml:space="preserve">Introdução de Modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VER</t>
+  </si>
+  <si>
     <t xml:space="preserve">Revisão</t>
   </si>
   <si>
-    <t xml:space="preserve">Falsa Falha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alto Fal. Retr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retor.Campo</t>
+    <t xml:space="preserve">FF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falha Falsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AF RET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto Falante Retrabalho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retorno de Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
   </si>
   <si>
     <t xml:space="preserve">Armazenamento</t>
   </si>
   <si>
-    <t xml:space="preserve">RC</t>
-  </si>
-  <si>
     <t xml:space="preserve">RV</t>
   </si>
   <si>
-    <t xml:space="preserve">Retorn.Técn Clente</t>
+    <t xml:space="preserve">Retorno de Vendas</t>
   </si>
 </sst>
 </file>
@@ -169,11 +199,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C1048576"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="23.41"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -183,119 +213,135 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
+        <v>25</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
